--- a/runtime/reports/result.xlsx
+++ b/runtime/reports/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,85 +439,130 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>候选来源</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>百度原始URL</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>百度原始排名</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>候选原文件</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>候选原路径</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>输出文件</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>输出路径</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>是否触发百度</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>本地有效候选数</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>百度返回URL数</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>百度下载成功数</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>百度过滤后有效数</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>低候选多样性提醒</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
         <is>
           <t>CLIP原始分</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>pHash距离</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>样图类别</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>候选类别</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>候选类别分</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>构图相似</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>造型相似</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>色彩相似</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>纹理相似</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>多维分组分</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>任务状态</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>本组最低质量门槛</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>分数已校准</t>
         </is>
@@ -544,67 +589,98 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>图 (3).png</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图 (3).png</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>0001_A.png</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0001_1 (1)\0001_A.png</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>11</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
         <v>0.763968</v>
       </c>
-      <c r="J2" t="n">
+      <c r="S2" t="n">
         <v>26</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="V2" t="n">
         <v>0.26382</v>
       </c>
-      <c r="N2" t="n">
+      <c r="W2" t="n">
         <v>0.6395690000000001</v>
       </c>
-      <c r="O2" t="n">
+      <c r="X2" t="n">
         <v>0.446714</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Y2" t="n">
         <v>0.842276</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Z2" t="n">
         <v>0.997283</v>
       </c>
-      <c r="R2" t="n">
+      <c r="AA2" t="n">
         <v>0.560636</v>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>0.519499</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="AC2" t="n">
+        <v>0.534778</v>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -631,67 +707,98 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>图 (9).png</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图 (9).png</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>0001_B.png</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0001_1 (1)\0001_B.png</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
         <v>0.640581</v>
       </c>
-      <c r="J3" t="n">
+      <c r="S3" t="n">
         <v>34</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="V3" t="n">
         <v>0.274552</v>
       </c>
-      <c r="N3" t="n">
+      <c r="W3" t="n">
         <v>0.279643</v>
       </c>
-      <c r="O3" t="n">
+      <c r="X3" t="n">
         <v>0.36646</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Y3" t="n">
         <v>0.771892</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Z3" t="n">
         <v>0.995356</v>
       </c>
-      <c r="R3" t="n">
+      <c r="AA3" t="n">
         <v>0.5768489999999999</v>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>0.519499</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="AC3" t="n">
+        <v>0.534778</v>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -718,67 +825,98 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>图 (15).png</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图 (15).png</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>0001_C.png</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0001_1 (1)\0001_C.png</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>11</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
         <v>0.632814</v>
       </c>
-      <c r="J4" t="n">
+      <c r="S4" t="n">
         <v>32</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="M4" t="n">
+      <c r="V4" t="n">
         <v>0.283076</v>
       </c>
-      <c r="N4" t="n">
+      <c r="W4" t="n">
         <v>0.542169</v>
       </c>
-      <c r="O4" t="n">
+      <c r="X4" t="n">
         <v>0.401807</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Y4" t="n">
         <v>0.809493</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Z4" t="n">
         <v>0.998545</v>
       </c>
-      <c r="R4" t="n">
+      <c r="AA4" t="n">
         <v>0.5313290000000001</v>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>0.519499</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="AC4" t="n">
+        <v>0.534778</v>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -805,67 +943,98 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>图 (34).png</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图 (34).png</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>0002_A.png</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0002_1 (2)\0002_A.png</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>14</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
         <v>0.640188</v>
       </c>
-      <c r="J5" t="n">
+      <c r="S5" t="n">
         <v>26</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="V5" t="n">
         <v>0.29816</v>
       </c>
-      <c r="N5" t="n">
+      <c r="W5" t="n">
         <v>0.6260289999999999</v>
       </c>
-      <c r="O5" t="n">
+      <c r="X5" t="n">
         <v>0.4115</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Y5" t="n">
         <v>0.645885</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Z5" t="n">
         <v>0.996683</v>
       </c>
-      <c r="R5" t="n">
+      <c r="AA5" t="n">
         <v>0.5209819999999999</v>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="AC5" t="n">
+        <v>0.503999</v>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -892,67 +1061,98 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>图 (36).png</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图 (36).png</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>0002_B.png</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0002_1 (2)\0002_B.png</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>14</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
         <v>0.614938</v>
       </c>
-      <c r="J6" t="n">
+      <c r="S6" t="n">
         <v>30</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="V6" t="n">
         <v>0.290079</v>
       </c>
-      <c r="N6" t="n">
+      <c r="W6" t="n">
         <v>0.414749</v>
       </c>
-      <c r="O6" t="n">
+      <c r="X6" t="n">
         <v>0.306109</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Y6" t="n">
         <v>0.578485</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Z6" t="n">
         <v>0.996849</v>
       </c>
-      <c r="R6" t="n">
+      <c r="AA6" t="n">
         <v>0.560453</v>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="AC6" t="n">
+        <v>0.503999</v>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -979,67 +1179,98 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>图 (8).png</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图 (8).png</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>0002_C.png</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0002_1 (2)\0002_C.png</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>14</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
         <v>0.719998</v>
       </c>
-      <c r="J7" t="n">
+      <c r="S7" t="n">
         <v>30</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="V7" t="n">
         <v>0.275558</v>
       </c>
-      <c r="N7" t="n">
+      <c r="W7" t="n">
         <v>0.431958</v>
       </c>
-      <c r="O7" t="n">
+      <c r="X7" t="n">
         <v>0.483842</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Y7" t="n">
         <v>0.924279</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Z7" t="n">
         <v>0.996729</v>
       </c>
-      <c r="R7" t="n">
+      <c r="AA7" t="n">
         <v>0.5823430000000001</v>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="AC7" t="n">
+        <v>0.503999</v>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1066,67 +1297,98 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>图75 (6).webp</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图75 (6).webp</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>0003_A.webp</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0003_1 (3)\0003_A.webp</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
         <v>0.581762</v>
       </c>
-      <c r="J8" t="n">
+      <c r="S8" t="n">
         <v>36</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="V8" t="n">
         <v>0.296992</v>
       </c>
-      <c r="N8" t="n">
+      <c r="W8" t="n">
         <v>0.506198</v>
       </c>
-      <c r="O8" t="n">
+      <c r="X8" t="n">
         <v>0.429569</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Y8" t="n">
         <v>0.925967</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Z8" t="n">
         <v>0.992852</v>
       </c>
-      <c r="R8" t="n">
+      <c r="AA8" t="n">
         <v>0.447479</v>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T8" t="n">
+      <c r="AC8" t="n">
         <v>0.5</v>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1153,67 +1415,98 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>26</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>图75 (4).webp</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图75 (4).webp</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>0003_B.webp</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0003_1 (3)\0003_B.webp</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
         <v>0.533154</v>
       </c>
-      <c r="J9" t="n">
+      <c r="S9" t="n">
         <v>30</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="M9" t="n">
+      <c r="V9" t="n">
         <v>0.263446</v>
       </c>
-      <c r="N9" t="n">
+      <c r="W9" t="n">
         <v>0.416438</v>
       </c>
-      <c r="O9" t="n">
+      <c r="X9" t="n">
         <v>0.351191</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Y9" t="n">
         <v>0.897115</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Z9" t="n">
         <v>0.991598</v>
       </c>
-      <c r="R9" t="n">
+      <c r="AA9" t="n">
         <v>0.488957</v>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T9" t="n">
+      <c r="AC9" t="n">
         <v>0.5</v>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1240,67 +1533,98 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>24</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>图 (33).png</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图 (33).png</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>0003_C.png</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0003_1 (3)\0003_C.png</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
         <v>0.539873</v>
       </c>
-      <c r="J10" t="n">
+      <c r="S10" t="n">
         <v>26</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="M10" t="n">
+      <c r="V10" t="n">
         <v>0.293308</v>
       </c>
-      <c r="N10" t="n">
+      <c r="W10" t="n">
         <v>0.524025</v>
       </c>
-      <c r="O10" t="n">
+      <c r="X10" t="n">
         <v>0.38035</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Y10" t="n">
         <v>0.736208</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Z10" t="n">
         <v>0.997918</v>
       </c>
-      <c r="R10" t="n">
+      <c r="AA10" t="n">
         <v>0.480421</v>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T10" t="n">
+      <c r="AC10" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1327,67 +1651,98 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>图 (12).png</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图 (12).png</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>0004_A.png</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0004_1 (4)\0004_A.png</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>9</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
         <v>0.726555</v>
       </c>
-      <c r="J11" t="n">
+      <c r="S11" t="n">
         <v>26</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>storage_cabinet</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>storage_cabinet</t>
         </is>
       </c>
-      <c r="M11" t="n">
+      <c r="V11" t="n">
         <v>0.314242</v>
       </c>
-      <c r="N11" t="n">
+      <c r="W11" t="n">
         <v>0.623267</v>
       </c>
-      <c r="O11" t="n">
+      <c r="X11" t="n">
         <v>0.406124</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Y11" t="n">
         <v>0.963157</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Z11" t="n">
         <v>0.995211</v>
       </c>
-      <c r="R11" t="n">
+      <c r="AA11" t="n">
         <v>0.525621</v>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="AC11" t="n">
+        <v>0.508588</v>
+      </c>
+      <c r="AD11" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1414,67 +1769,98 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>图76 (3).webp</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图76 (3).webp</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>0004_B.webp</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0004_1 (4)\0004_B.webp</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
         <v>0.562387</v>
       </c>
-      <c r="J12" t="n">
+      <c r="S12" t="n">
         <v>36</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>storage_cabinet</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>storage_cabinet</t>
         </is>
       </c>
-      <c r="M12" t="n">
+      <c r="V12" t="n">
         <v>0.300696</v>
       </c>
-      <c r="N12" t="n">
+      <c r="W12" t="n">
         <v>0.278912</v>
       </c>
-      <c r="O12" t="n">
+      <c r="X12" t="n">
         <v>0.350397</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Y12" t="n">
         <v>0.664417</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Z12" t="n">
         <v>0.997849</v>
       </c>
-      <c r="R12" t="n">
+      <c r="AA12" t="n">
         <v>0.5481819999999999</v>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="AC12" t="n">
+        <v>0.508588</v>
+      </c>
+      <c r="AD12" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1501,67 +1887,98 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>图 (14).png</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图 (14).png</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>0004_C.png</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0004_1 (4)\0004_C.png</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>9</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
         <v>0.671381</v>
       </c>
-      <c r="J13" t="n">
+      <c r="S13" t="n">
         <v>28</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>storage_cabinet</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>storage_cabinet</t>
         </is>
       </c>
-      <c r="M13" t="n">
+      <c r="V13" t="n">
         <v>0.286442</v>
       </c>
-      <c r="N13" t="n">
+      <c r="W13" t="n">
         <v>0.555244</v>
       </c>
-      <c r="O13" t="n">
+      <c r="X13" t="n">
         <v>0.426907</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Y13" t="n">
         <v>0.828037</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Z13" t="n">
         <v>0.994202</v>
       </c>
-      <c r="R13" t="n">
+      <c r="AA13" t="n">
         <v>0.551515</v>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U13" t="inlineStr">
+      <c r="AC13" t="n">
+        <v>0.508588</v>
+      </c>
+      <c r="AD13" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1588,67 +2005,98 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>图 (25).png</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图 (25).png</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>0005_A.png</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0005_1 (5)\0005_A.png</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
         <v>0.830287</v>
       </c>
-      <c r="J14" t="n">
+      <c r="S14" t="n">
         <v>30</v>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>kitchen_sink</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>kitchen_sink</t>
         </is>
       </c>
-      <c r="M14" t="n">
+      <c r="V14" t="n">
         <v>0.319284</v>
       </c>
-      <c r="N14" t="n">
+      <c r="W14" t="n">
         <v>0.5418500000000001</v>
       </c>
-      <c r="O14" t="n">
+      <c r="X14" t="n">
         <v>0.389973</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Y14" t="n">
         <v>0.849499</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Z14" t="n">
         <v>0.998545</v>
       </c>
-      <c r="R14" t="n">
+      <c r="AA14" t="n">
         <v>0.542547</v>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T14" t="n">
-        <v>0.564595</v>
-      </c>
-      <c r="U14" t="inlineStr">
+      <c r="AC14" t="n">
+        <v>0.581201</v>
+      </c>
+      <c r="AD14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1675,67 +2123,98 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>图 (23).png</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图 (23).png</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>0005_B.png</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0005_1 (5)\0005_B.png</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>5</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
         <v>0.707613</v>
       </c>
-      <c r="J15" t="n">
+      <c r="S15" t="n">
         <v>32</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>kitchen_sink</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>kitchen_sink</t>
         </is>
       </c>
-      <c r="M15" t="n">
+      <c r="V15" t="n">
         <v>0.343915</v>
       </c>
-      <c r="N15" t="n">
+      <c r="W15" t="n">
         <v>0.459588</v>
       </c>
-      <c r="O15" t="n">
+      <c r="X15" t="n">
         <v>0.375606</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Y15" t="n">
         <v>0.786883</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Z15" t="n">
         <v>0.997153</v>
       </c>
-      <c r="R15" t="n">
+      <c r="AA15" t="n">
         <v>0.5717449999999999</v>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T15" t="n">
-        <v>0.564595</v>
-      </c>
-      <c r="U15" t="inlineStr">
+      <c r="AC15" t="n">
+        <v>0.581201</v>
+      </c>
+      <c r="AD15" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1762,67 +2241,98 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>图 (22).png</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图 (22).png</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>0005_C.png</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0005_1 (5)\0005_C.png</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>5</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
         <v>0.687277</v>
       </c>
-      <c r="J16" t="n">
+      <c r="S16" t="n">
         <v>30</v>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>kitchen_sink</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>kitchen_sink</t>
         </is>
       </c>
-      <c r="M16" t="n">
+      <c r="V16" t="n">
         <v>0.253263</v>
       </c>
-      <c r="N16" t="n">
+      <c r="W16" t="n">
         <v>0.513169</v>
       </c>
-      <c r="O16" t="n">
+      <c r="X16" t="n">
         <v>0.362391</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Y16" t="n">
         <v>0.803633</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Z16" t="n">
         <v>0.992684</v>
       </c>
-      <c r="R16" t="n">
+      <c r="AA16" t="n">
         <v>0.57445</v>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T16" t="n">
-        <v>0.564595</v>
-      </c>
-      <c r="U16" t="inlineStr">
+      <c r="AC16" t="n">
+        <v>0.581201</v>
+      </c>
+      <c r="AD16" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1849,67 +2359,102 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>图 (21).png</t>
+          <t>baidu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图 (21).png</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0006_A.png</t>
-        </is>
+          <t>http://mms1.baidu.com/it/u=97018891,2425667346&amp;fm=253&amp;app=138&amp;f=JPEG?w=666&amp;h=500</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>10</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>C:\Users\mozhihao\core\image-hybrid-search\output\0006_1 (6)\0006_A.png</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>0.757452</v>
-      </c>
-      <c r="J17" t="n">
-        <v>28</v>
+          <t>99c2413cb87fb54dc52d7aad8377042b805e36da378ce8c626687dd3e59bbbd7.jpg</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>C:\Users\mozhihao\core\image-hybrid-search\runtime\baidu_cache\99c2413cb87fb54dc52d7aad8377042b805e36da378ce8c626687dd3e59bbbd7.jpg</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0006_A.jpg</t>
+        </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t>C:\Users\mozhihao\core\image-hybrid-search\output\0006_1 (6)\0006_A.jpg</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" t="n">
+        <v>30</v>
+      </c>
+      <c r="O17" t="n">
+        <v>10</v>
+      </c>
+      <c r="P17" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>0.8478830000000001</v>
+      </c>
+      <c r="S17" t="n">
+        <v>32</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
           <t>kitchen_sink</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>kitchen_sink</t>
         </is>
       </c>
-      <c r="M17" t="n">
-        <v>0.314679</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.482147</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.350437</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.8964800000000001</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.993855</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.488064</v>
-      </c>
-      <c r="S17" t="inlineStr">
+      <c r="V17" t="n">
+        <v>0.326744</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.58352</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.340164</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.97403</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.998371</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.541918</v>
+      </c>
+      <c r="AB17" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T17" t="n">
-        <v>0.5150670000000001</v>
-      </c>
-      <c r="U17" t="inlineStr">
+      <c r="AC17" t="n">
+        <v>0.530216</v>
+      </c>
+      <c r="AD17" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1936,67 +2481,102 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>图75 (2).webp</t>
+          <t>baidu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图75 (2).webp</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0006_B.webp</t>
-        </is>
+          <t>http://mms0.baidu.com/it/u=2634100412,3518023982&amp;fm=253&amp;app=138&amp;f=JPEG?w=418&amp;h=313</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>7</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>C:\Users\mozhihao\core\image-hybrid-search\output\0006_1 (6)\0006_B.webp</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>0.552947</v>
-      </c>
-      <c r="J18" t="n">
-        <v>24</v>
+          <t>4151e344f57f7b8b4b2d207fcd88c4614f463a634e2e8f60cb75226b978041b9.jpg</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>C:\Users\mozhihao\core\image-hybrid-search\runtime\baidu_cache\4151e344f57f7b8b4b2d207fcd88c4614f463a634e2e8f60cb75226b978041b9.jpg</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0006_B.jpg</t>
+        </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t>C:\Users\mozhihao\core\image-hybrid-search\output\0006_1 (6)\0006_B.jpg</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N18" t="n">
+        <v>30</v>
+      </c>
+      <c r="O18" t="n">
+        <v>10</v>
+      </c>
+      <c r="P18" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>0.799913</v>
+      </c>
+      <c r="S18" t="n">
+        <v>32</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
           <t>kitchen_sink</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>kitchen_cabinet</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
-        <v>0.268341</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.465645</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.249991</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0.811615</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.9982259999999999</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.510108</v>
-      </c>
-      <c r="S18" t="inlineStr">
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>kitchen_sink</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>0.297582</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.5561430000000001</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.353995</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.923596</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.99765</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.591535</v>
+      </c>
+      <c r="AB18" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T18" t="n">
-        <v>0.5150670000000001</v>
-      </c>
-      <c r="U18" t="inlineStr">
+      <c r="AC18" t="n">
+        <v>0.530216</v>
+      </c>
+      <c r="AD18" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2023,67 +2603,98 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>图74 (10).png</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图74 (10).png</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>图 (21).png</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图 (21).png</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>0006_C.png</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0006_1 (6)\0006_C.png</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>0.522942</v>
-      </c>
-      <c r="J19" t="n">
-        <v>32</v>
-      </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" t="n">
+        <v>30</v>
+      </c>
+      <c r="O19" t="n">
+        <v>10</v>
+      </c>
+      <c r="P19" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>0.757452</v>
+      </c>
+      <c r="S19" t="n">
+        <v>28</v>
+      </c>
+      <c r="T19" t="inlineStr">
         <is>
           <t>kitchen_sink</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>kitchen_cabinet</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
-        <v>0.248831</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.55085</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.384232</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.775586</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.99797</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.463387</v>
-      </c>
-      <c r="S19" t="inlineStr">
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>kitchen_sink</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>0.314679</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.482147</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.350437</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.8964800000000001</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.993855</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.61731</v>
+      </c>
+      <c r="AB19" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T19" t="n">
-        <v>0.5150670000000001</v>
-      </c>
-      <c r="U19" t="inlineStr">
+      <c r="AC19" t="n">
+        <v>0.530216</v>
+      </c>
+      <c r="AD19" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2110,67 +2721,98 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>图 (43).png</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图 (43).png</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>0007_A.png</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0007_1 (7)\0007_A.png</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>7</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
         <v>0.869138</v>
       </c>
-      <c r="J20" t="n">
+      <c r="S20" t="n">
         <v>26</v>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="M20" t="n">
+      <c r="V20" t="n">
         <v>0.273857</v>
       </c>
-      <c r="N20" t="n">
+      <c r="W20" t="n">
         <v>0.749144</v>
       </c>
-      <c r="O20" t="n">
+      <c r="X20" t="n">
         <v>0.426726</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Y20" t="n">
         <v>0.576766</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Z20" t="n">
         <v>0.997868</v>
       </c>
-      <c r="R20" t="n">
+      <c r="AA20" t="n">
         <v>0.646189</v>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T20" t="n">
-        <v>0.63933</v>
-      </c>
-      <c r="U20" t="inlineStr">
+      <c r="AC20" t="n">
+        <v>0.658134</v>
+      </c>
+      <c r="AD20" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2197,67 +2839,98 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>图 (38).png</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图 (38).png</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>0007_B.png</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0007_1 (7)\0007_B.png</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>7</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
         <v>0.940192</v>
       </c>
-      <c r="J21" t="n">
+      <c r="S21" t="n">
         <v>32</v>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="M21" t="n">
+      <c r="V21" t="n">
         <v>0.28495</v>
       </c>
-      <c r="N21" t="n">
+      <c r="W21" t="n">
         <v>0.44896</v>
       </c>
-      <c r="O21" t="n">
+      <c r="X21" t="n">
         <v>0.437028</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Y21" t="n">
         <v>0.82787</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Z21" t="n">
         <v>0.9975579999999999</v>
       </c>
-      <c r="R21" t="n">
+      <c r="AA21" t="n">
         <v>0.677843</v>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T21" t="n">
-        <v>0.63933</v>
-      </c>
-      <c r="U21" t="inlineStr">
+      <c r="AC21" t="n">
+        <v>0.658134</v>
+      </c>
+      <c r="AD21" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2284,67 +2957,98 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>图 (42).png</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图 (42).png</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>0007_C.png</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0007_1 (7)\0007_C.png</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>7</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
         <v>0.882426</v>
       </c>
-      <c r="J22" t="n">
+      <c r="S22" t="n">
         <v>24</v>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="M22" t="n">
+      <c r="V22" t="n">
         <v>0.274639</v>
       </c>
-      <c r="N22" t="n">
+      <c r="W22" t="n">
         <v>0.551485</v>
       </c>
-      <c r="O22" t="n">
+      <c r="X22" t="n">
         <v>0.40224</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Y22" t="n">
         <v>0.479859</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Z22" t="n">
         <v>0.998372</v>
       </c>
-      <c r="R22" t="n">
+      <c r="AA22" t="n">
         <v>0.717337</v>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T22" t="n">
-        <v>0.63933</v>
-      </c>
-      <c r="U22" t="inlineStr">
+      <c r="AC22" t="n">
+        <v>0.658134</v>
+      </c>
+      <c r="AD22" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2371,67 +3075,98 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>7</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>图 (39).png</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图 (39).png</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>0008_A.png</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0008_1 (8)\0008_A.png</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
         <v>0.732743</v>
       </c>
-      <c r="J23" t="n">
+      <c r="S23" t="n">
         <v>30</v>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="M23" t="n">
+      <c r="V23" t="n">
         <v>0.284125</v>
       </c>
-      <c r="N23" t="n">
+      <c r="W23" t="n">
         <v>0.7429789999999999</v>
       </c>
-      <c r="O23" t="n">
+      <c r="X23" t="n">
         <v>0.364774</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Y23" t="n">
         <v>0.472271</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Z23" t="n">
         <v>0.998369</v>
       </c>
-      <c r="R23" t="n">
+      <c r="AA23" t="n">
         <v>0.59201</v>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T23" t="n">
-        <v>0.585604</v>
-      </c>
-      <c r="U23" t="inlineStr">
+      <c r="AC23" t="n">
+        <v>0.602828</v>
+      </c>
+      <c r="AD23" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2458,67 +3193,98 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>图 (32).png</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图 (32).png</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>0008_B.png</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0008_1 (8)\0008_B.png</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>5</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
         <v>0.861183</v>
       </c>
-      <c r="J24" t="n">
+      <c r="S24" t="n">
         <v>34</v>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="M24" t="n">
+      <c r="V24" t="n">
         <v>0.27405</v>
       </c>
-      <c r="N24" t="n">
+      <c r="W24" t="n">
         <v>0.463634</v>
       </c>
-      <c r="O24" t="n">
+      <c r="X24" t="n">
         <v>0.353866</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Y24" t="n">
         <v>0.7204700000000001</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Z24" t="n">
         <v>0.997564</v>
       </c>
-      <c r="R24" t="n">
+      <c r="AA24" t="n">
         <v>0.655932</v>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T24" t="n">
-        <v>0.585604</v>
-      </c>
-      <c r="U24" t="inlineStr">
+      <c r="AC24" t="n">
+        <v>0.602828</v>
+      </c>
+      <c r="AD24" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2545,67 +3311,98 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>14</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>图73 (4).png</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图73 (4).png</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>0008_C.png</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0008_1 (8)\0008_C.png</t>
         </is>
       </c>
-      <c r="I25" t="n">
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>5</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R25" t="n">
         <v>0.641493</v>
       </c>
-      <c r="J25" t="n">
+      <c r="S25" t="n">
         <v>24</v>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>living_room</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>furniture</t>
         </is>
       </c>
-      <c r="M25" t="n">
+      <c r="V25" t="n">
         <v>0.249267</v>
       </c>
-      <c r="N25" t="n">
+      <c r="W25" t="n">
         <v>0.507397</v>
       </c>
-      <c r="O25" t="n">
+      <c r="X25" t="n">
         <v>0.283282</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Y25" t="n">
         <v>0.164331</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Z25" t="n">
         <v>0.997714</v>
       </c>
-      <c r="R25" t="n">
+      <c r="AA25" t="n">
         <v>0.600749</v>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T25" t="n">
-        <v>0.585604</v>
-      </c>
-      <c r="U25" t="inlineStr">
+      <c r="AC25" t="n">
+        <v>0.602828</v>
+      </c>
+      <c r="AD25" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2632,67 +3429,98 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>10</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>图 (68).png</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图 (68).png</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>0009_A.png</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0009_1 (9)\0009_A.png</t>
         </is>
       </c>
-      <c r="I26" t="n">
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>7</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
         <v>0.686009</v>
       </c>
-      <c r="J26" t="n">
+      <c r="S26" t="n">
         <v>30</v>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>cleaning</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>cleaning</t>
         </is>
       </c>
-      <c r="M26" t="n">
+      <c r="V26" t="n">
         <v>0.219818</v>
       </c>
-      <c r="N26" t="n">
+      <c r="W26" t="n">
         <v>0.781366</v>
       </c>
-      <c r="O26" t="n">
+      <c r="X26" t="n">
         <v>0.613488</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Y26" t="n">
         <v>0.856374</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Z26" t="n">
         <v>0.997677</v>
       </c>
-      <c r="R26" t="n">
+      <c r="AA26" t="n">
         <v>0.6081569999999999</v>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T26" t="n">
+      <c r="AC26" t="n">
         <v>0.5</v>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="AD26" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2719,67 +3547,98 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>12</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
           <t>图 (70).png</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图 (70).png</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>0009_B.png</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0009_1 (9)\0009_B.png</t>
         </is>
       </c>
-      <c r="I27" t="n">
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>7</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
         <v>0.675974</v>
       </c>
-      <c r="J27" t="n">
+      <c r="S27" t="n">
         <v>34</v>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>cleaning</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>cleaning</t>
         </is>
       </c>
-      <c r="M27" t="n">
+      <c r="V27" t="n">
         <v>0.195042</v>
       </c>
-      <c r="N27" t="n">
+      <c r="W27" t="n">
         <v>0.235704</v>
       </c>
-      <c r="O27" t="n">
+      <c r="X27" t="n">
         <v>0.521621</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Y27" t="n">
         <v>0.599648</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Z27" t="n">
         <v>0.993546</v>
       </c>
-      <c r="R27" t="n">
+      <c r="AA27" t="n">
         <v>0.593114</v>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T27" t="n">
+      <c r="AC27" t="n">
         <v>0.5</v>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="AD27" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2806,67 +3665,98 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
           <t>图 (45).png</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图 (45).png</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>0009_C.png</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0009_1 (9)\0009_C.png</t>
         </is>
       </c>
-      <c r="I28" t="n">
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>7</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
         <v>0.711821</v>
       </c>
-      <c r="J28" t="n">
+      <c r="S28" t="n">
         <v>28</v>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>cleaning</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>cleaning</t>
         </is>
       </c>
-      <c r="M28" t="n">
+      <c r="V28" t="n">
         <v>0.197377</v>
       </c>
-      <c r="N28" t="n">
+      <c r="W28" t="n">
         <v>0.624758</v>
       </c>
-      <c r="O28" t="n">
+      <c r="X28" t="n">
         <v>0.586979</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Y28" t="n">
         <v>0.583029</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="Z28" t="n">
         <v>0.9968320000000001</v>
       </c>
-      <c r="R28" t="n">
+      <c r="AA28" t="n">
         <v>0.57302</v>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T28" t="n">
+      <c r="AC28" t="n">
         <v>0.5</v>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="AD28" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2893,67 +3783,98 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>图74 (5).png</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图74 (5).png</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>0010_A.png</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0010_1 (10)\0010_A.png</t>
         </is>
       </c>
-      <c r="I29" t="n">
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>7</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
         <v>0.824589</v>
       </c>
-      <c r="J29" t="n">
+      <c r="S29" t="n">
         <v>30</v>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>kitchen_cabinet</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>kitchen_cabinet</t>
         </is>
       </c>
-      <c r="M29" t="n">
+      <c r="V29" t="n">
         <v>0.248333</v>
       </c>
-      <c r="N29" t="n">
+      <c r="W29" t="n">
         <v>0.541999</v>
       </c>
-      <c r="O29" t="n">
+      <c r="X29" t="n">
         <v>0.529083</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Y29" t="n">
         <v>0.871158</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="Z29" t="n">
         <v>0.998456</v>
       </c>
-      <c r="R29" t="n">
+      <c r="AA29" t="n">
         <v>0.566801</v>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T29" t="n">
-        <v>0.560721</v>
-      </c>
-      <c r="U29" t="inlineStr">
+      <c r="AC29" t="n">
+        <v>0.5772119999999999</v>
+      </c>
+      <c r="AD29" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -2980,67 +3901,98 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>图74 (6).png</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图74 (6).png</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>图74 (10).png</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图74 (10).png</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>0010_B.png</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0010_1 (10)\0010_B.png</t>
         </is>
       </c>
-      <c r="I30" t="n">
-        <v>0.805123</v>
-      </c>
-      <c r="J30" t="n">
-        <v>30</v>
-      </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>7</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R30" t="n">
+        <v>0.807673</v>
+      </c>
+      <c r="S30" t="n">
+        <v>32</v>
+      </c>
+      <c r="T30" t="inlineStr">
         <is>
           <t>kitchen_cabinet</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>kitchen_cabinet</t>
         </is>
       </c>
-      <c r="M30" t="n">
-        <v>0.232695</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0.525213</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0.496887</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0.947222</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0.998848</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0.57703</v>
-      </c>
-      <c r="S30" t="inlineStr">
+      <c r="V30" t="n">
+        <v>0.248831</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.480874</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.51293</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.834452</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.998545</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.593247</v>
+      </c>
+      <c r="AB30" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T30" t="n">
-        <v>0.560721</v>
-      </c>
-      <c r="U30" t="inlineStr">
+      <c r="AC30" t="n">
+        <v>0.5772119999999999</v>
+      </c>
+      <c r="AD30" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -3067,67 +4019,98 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>图74 (7).png</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图74 (7).png</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
+          <t>local</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>图74 (6).png</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>C:\Users\mozhihao\core\image-hybrid-search\candidate_library\图74 (6).png</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>0010_C.png</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>C:\Users\mozhihao\core\image-hybrid-search\output\0010_1 (10)\0010_C.png</t>
         </is>
       </c>
-      <c r="I31" t="n">
-        <v>0.778285</v>
-      </c>
-      <c r="J31" t="n">
-        <v>36</v>
-      </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>7</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>0.805123</v>
+      </c>
+      <c r="S31" t="n">
+        <v>30</v>
+      </c>
+      <c r="T31" t="inlineStr">
         <is>
           <t>kitchen_cabinet</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>storage_cabinet</t>
-        </is>
-      </c>
-      <c r="M31" t="n">
-        <v>0.225958</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0.459818</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0.5296999999999999</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0.974542</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0.998135</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0.6089830000000001</v>
-      </c>
-      <c r="S31" t="inlineStr">
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>kitchen_cabinet</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>0.232695</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.525213</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.496887</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.947222</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.998848</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.625165</v>
+      </c>
+      <c r="AB31" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
       </c>
-      <c r="T31" t="n">
-        <v>0.560721</v>
-      </c>
-      <c r="U31" t="inlineStr">
+      <c r="AC31" t="n">
+        <v>0.5772119999999999</v>
+      </c>
+      <c r="AD31" t="inlineStr">
         <is>
           <t>否</t>
         </is>
